--- a/Results/pam_parametrizer_diagnostics_.xlsx
+++ b/Results/pam_parametrizer_diagnostics_.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="19">
   <si>
     <t>run_id</t>
   </si>
@@ -24,6 +24,9 @@
     <t>enzyme_id</t>
   </si>
   <si>
+    <t>direction</t>
+  </si>
+  <si>
     <t>rxn_id</t>
   </si>
   <si>
@@ -45,7 +48,10 @@
     <t>E5</t>
   </si>
   <si>
-    <t>E4</t>
+    <t>f</t>
+  </si>
+  <si>
+    <t>b</t>
   </si>
   <si>
     <t>R1</t>
@@ -58,9 +64,6 @@
   </si>
   <si>
     <t>R5</t>
-  </si>
-  <si>
-    <t>R4</t>
   </si>
   <si>
     <t>time_s</t>
@@ -427,10 +430,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -446,25 +449,31 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2">
-        <v>1</v>
+      <c r="D2" t="s">
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>0.5252677507619506</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>0.5557117782737089</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -474,14 +483,17 @@
       <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="D3">
-        <v>0.09691628392429542</v>
+      <c r="D3" t="s">
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>0.5252677507619506</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>1</v>
       </c>
@@ -489,50 +501,59 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>0.5252677507619506</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>4.429397125041991</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <v>10.96910874594336</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
         <v>10</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>0.5252676867811511</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>0.9804720535222615</v>
+      <c r="D6" t="s">
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>0.5252676867811511</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>0.6660361980555147</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>1</v>
       </c>
@@ -540,84 +561,99 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>277.7777777777778</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
         <v>13</v>
       </c>
-      <c r="D7">
-        <v>1.655289639434912</v>
-      </c>
-      <c r="E7">
-        <v>0.5252676867811511</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="E9">
+        <v>25.32364152926341</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
         <v>10</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>0.527502129831416</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9">
-        <v>0.3108395116247901</v>
-      </c>
-      <c r="E9">
-        <v>0.527502129831416</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>2</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10">
-        <v>0.5604464462904065</v>
+      <c r="D10" t="s">
+        <v>15</v>
       </c>
       <c r="E10">
-        <v>0.527502129831416</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
       </c>
       <c r="E11">
-        <v>0.7515005480143815</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>3</v>
       </c>
@@ -627,116 +663,137 @@
       <c r="C12" t="s">
         <v>11</v>
       </c>
-      <c r="D12">
-        <v>0.4013695795472748</v>
+      <c r="D12" t="s">
+        <v>12</v>
       </c>
       <c r="E12">
-        <v>0.7515005480143815</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>2.14918257905273</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>3</v>
       </c>
       <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13">
+        <v>217.4841778500384</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
         <v>9</v>
       </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13">
-        <v>0.0003908538804303641</v>
-      </c>
-      <c r="E13">
-        <v>0.7515005480143815</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
       <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14">
-        <v>1.960944107044523</v>
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
       </c>
       <c r="E14">
-        <v>0.7581137964134667</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>2784.575910439737</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B15" t="s">
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15">
-        <v>0.7529059363941781</v>
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
       </c>
       <c r="E15">
-        <v>0.7581137964134667</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>12.24163984779919</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16">
-        <v>0.0007708067027087771</v>
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
       </c>
       <c r="E16">
-        <v>0.7581137964134667</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>0.6936064701295868</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
       </c>
-      <c r="D17">
-        <v>1.972109633042538</v>
+      <c r="D17" t="s">
+        <v>13</v>
       </c>
       <c r="E17">
-        <v>0.5252676867811511</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
       </c>
-      <c r="D18">
-        <v>0.5000000000000001</v>
+      <c r="D18" t="s">
+        <v>13</v>
       </c>
       <c r="E18">
-        <v>0.5252676867811511</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>0</v>
       </c>
@@ -744,33 +801,39 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19">
-        <v>0.45</v>
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>14</v>
       </c>
       <c r="E19">
-        <v>0.5252676867811511</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20">
-        <v>1.972109633042538</v>
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>14</v>
       </c>
       <c r="E20">
-        <v>0.5252676869941332</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>0.9995469163113551</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>1</v>
       </c>
@@ -780,14 +843,17 @@
       <c r="C21" t="s">
         <v>11</v>
       </c>
-      <c r="D21">
-        <v>0.5000000000000001</v>
+      <c r="D21" t="s">
+        <v>12</v>
       </c>
       <c r="E21">
-        <v>0.5252676869941332</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>400.4832563425778</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>1</v>
       </c>
@@ -795,370 +861,416 @@
         <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
       </c>
       <c r="E22">
-        <v>0.5252676869941332</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>138.8888888888889</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
       </c>
-      <c r="D23">
-        <v>1.972109633042538</v>
+      <c r="D23" t="s">
+        <v>15</v>
       </c>
       <c r="E23">
-        <v>0.5252676869941332</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25" t="s">
         <v>6</v>
       </c>
-      <c r="C24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24">
-        <v>0.4773537030039671</v>
-      </c>
-      <c r="E24">
-        <v>0.5252676869941332</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>2</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25">
+        <v>0.6936064701295865</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26" t="s">
         <v>7</v>
       </c>
-      <c r="C25" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25">
-        <v>0.5604464462904069</v>
-      </c>
-      <c r="E25">
-        <v>0.5252676869941332</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>3</v>
-      </c>
-      <c r="B26" t="s">
-        <v>5</v>
-      </c>
       <c r="C26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26">
-        <v>1.094631770506291</v>
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
       </c>
       <c r="E26">
-        <v>0.5274284351124779</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
       </c>
-      <c r="D27">
-        <v>0.4773537030039671</v>
+      <c r="D27" t="s">
+        <v>15</v>
       </c>
       <c r="E27">
-        <v>0.5274284351124779</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>125</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>3</v>
       </c>
       <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28">
+        <v>400.4832563425779</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>3</v>
+      </c>
+      <c r="B29" t="s">
         <v>7</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29">
+        <v>142.8630057024533</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>3</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>1</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" t="s">
         <v>12</v>
       </c>
-      <c r="D28">
-        <v>0.05663166740504366</v>
-      </c>
-      <c r="E28">
-        <v>0.5274284351124779</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>4</v>
-      </c>
-      <c r="B29" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="E31">
+        <v>4.088727415528552</v>
+      </c>
+      <c r="F31">
+        <v>-465.8218814093863</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>1</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32">
+        <v>0.6936064701295868</v>
+      </c>
+      <c r="F32">
+        <v>-465.8218814093863</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>1</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" t="s">
         <v>10</v>
       </c>
-      <c r="D29">
-        <v>1.094631770506291</v>
-      </c>
-      <c r="E29">
-        <v>0.5274284351124779</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>4</v>
-      </c>
-      <c r="B30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30">
-        <v>0.4773537030039671</v>
-      </c>
-      <c r="E30">
-        <v>0.5274284351124779</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>4</v>
-      </c>
-      <c r="B31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="D33" t="s">
         <v>13</v>
       </c>
-      <c r="D31">
-        <v>0.45</v>
-      </c>
-      <c r="E31">
-        <v>0.5274284351124779</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>1</v>
-      </c>
-      <c r="B32" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32">
-        <v>0.527064665943998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>1</v>
-      </c>
-      <c r="B33" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33">
-        <v>0.5000000000000001</v>
-      </c>
       <c r="E33">
-        <v>0.527064665943998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>3.349180789622017</v>
+      </c>
+      <c r="F33">
+        <v>-465.8218814093863</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
         <v>13</v>
       </c>
-      <c r="D34">
-        <v>0.45</v>
-      </c>
       <c r="E34">
-        <v>0.527064665943998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>0.7904136153485284</v>
+      </c>
+      <c r="F34">
+        <v>-465.8218814093863</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C35" t="s">
         <v>10</v>
       </c>
-      <c r="D35">
-        <v>1</v>
+      <c r="D35" t="s">
+        <v>15</v>
       </c>
       <c r="E35">
-        <v>0.5270646659439979</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>27.97557678509626</v>
+      </c>
+      <c r="F35">
+        <v>-465.8218814093863</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="F36">
+        <v>-465.8218814093863</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>2</v>
+      </c>
+      <c r="B37" t="s">
         <v>6</v>
       </c>
-      <c r="C36" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36">
-        <v>0.5000000000000001</v>
-      </c>
-      <c r="E36">
-        <v>0.5270646659439979</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37">
-        <v>2</v>
-      </c>
-      <c r="B37" t="s">
-        <v>8</v>
-      </c>
       <c r="C37" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37">
+        <v>400.4832563425778</v>
+      </c>
+      <c r="F37">
+        <v>-465.8218814093863</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>2</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" t="s">
         <v>13</v>
       </c>
-      <c r="D37">
-        <v>0.45</v>
-      </c>
-      <c r="E37">
-        <v>0.5270646659439979</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38">
-        <v>3</v>
-      </c>
-      <c r="B38" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
       <c r="E38">
-        <v>0.5270646659439979</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>351.4334424202615</v>
+      </c>
+      <c r="F38">
+        <v>-465.8218814093863</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C39" t="s">
         <v>11</v>
       </c>
-      <c r="D39">
-        <v>0.5000000000000001</v>
+      <c r="D39" t="s">
+        <v>15</v>
       </c>
       <c r="E39">
-        <v>0.5270646659439979</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>125</v>
+      </c>
+      <c r="F39">
+        <v>-465.8218814093863</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40">
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40">
+        <v>0.6936064701295865</v>
+      </c>
+      <c r="F40">
+        <v>-465.8218814093863</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>3</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" t="s">
         <v>13</v>
       </c>
-      <c r="D40">
-        <v>0.45</v>
-      </c>
-      <c r="E40">
-        <v>0.5270646659439979</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41">
-        <v>4</v>
-      </c>
-      <c r="B41" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
       <c r="E41">
-        <v>0.5275470314612686</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>0.7904136153485284</v>
+      </c>
+      <c r="F41">
+        <v>-465.8218814093863</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
       </c>
-      <c r="D42">
-        <v>0.3696851965746978</v>
+      <c r="D42" t="s">
+        <v>15</v>
       </c>
       <c r="E42">
-        <v>0.5275470314612686</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43">
-        <v>4</v>
-      </c>
-      <c r="B43" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43">
-        <v>0.8441289241689384</v>
-      </c>
-      <c r="E43">
-        <v>0.5275470314612686</v>
+        <v>9.086060923396781</v>
+      </c>
+      <c r="F42">
+        <v>-465.8218814093863</v>
       </c>
     </row>
   </sheetData>
@@ -1168,7 +1280,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1176,10 +1288,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1187,153 +1299,109 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4.467663246003212</v>
+        <v>15.89535509399866</v>
       </c>
       <c r="C2">
-        <v>0.001241017568334226</v>
+        <v>0.004415376414999628</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>29.57675383300011</v>
+        <v>15.53606549100004</v>
       </c>
       <c r="C3">
-        <v>0.008215764953611142</v>
+        <v>0.004315573747500012</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>45.96237092299998</v>
+        <v>14.63511658999778</v>
       </c>
       <c r="C4">
-        <v>0.01276732525638888</v>
+        <v>0.004065310163888272</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>54.0219224020002</v>
+        <v>15.95927955500156</v>
       </c>
       <c r="C5">
-        <v>0.01500608955611117</v>
+        <v>0.004433133209722655</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B6">
-        <v>53.94769591799923</v>
+        <v>2.709200430999772</v>
       </c>
       <c r="C6">
-        <v>0.01498547108833312</v>
+        <v>0.0007525556752777144</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B7">
-        <v>47.06346838600075</v>
+        <v>2.475116861001879</v>
       </c>
       <c r="C7">
-        <v>0.01307318566277799</v>
+        <v>0.000687532461389411</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B8">
-        <v>29.12377588299933</v>
+        <v>2.350216724997154</v>
       </c>
       <c r="C8">
-        <v>0.00808993774527759</v>
+        <v>0.000652837979165876</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9">
-        <v>24.75478587600082</v>
+        <v>4.820158458998776</v>
       </c>
       <c r="C9">
-        <v>0.006876329410000229</v>
+        <v>0.001338932905277438</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10">
-        <v>20.62471128800098</v>
+        <v>4.077991112000745</v>
       </c>
       <c r="C10">
-        <v>0.005729086468889161</v>
+        <v>0.001132775308889096</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11">
-        <v>22.62750565199894</v>
+        <v>4.079633117999037</v>
       </c>
       <c r="C11">
-        <v>0.006285418236666373</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12">
-        <v>1</v>
-      </c>
-      <c r="B12">
-        <v>26.85211578899907</v>
-      </c>
-      <c r="C12">
-        <v>0.007458921052499742</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13">
-        <v>2</v>
-      </c>
-      <c r="B13">
-        <v>18.79541383000105</v>
-      </c>
-      <c r="C13">
-        <v>0.005220948286111403</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14">
-        <v>3</v>
-      </c>
-      <c r="B14">
-        <v>15.50464317700244</v>
-      </c>
-      <c r="C14">
-        <v>0.004306845326945121</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15">
-        <v>4</v>
-      </c>
-      <c r="B15">
-        <v>15.14412409600118</v>
-      </c>
-      <c r="C15">
-        <v>0.004206701137778105</v>
+        <v>0.001133231421666399</v>
       </c>
     </row>
   </sheetData>
@@ -1343,7 +1411,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1351,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1359,111 +1427,79 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>0.5252676869941333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>0.5087823562938095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>0.7515005479287782</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B6">
-        <v>0.758113796329178</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B7">
-        <v>0.5252676869941333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B8">
-        <v>0.5252676869941333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9">
-        <v>0.5252676869941333</v>
+        <v>-465.8218814093863</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10">
-        <v>0.5274284351124779</v>
+        <v>-465.8218814093863</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11">
-        <v>0.5274284351124779</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>1</v>
-      </c>
-      <c r="B12">
-        <v>0.527064665943998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
-        <v>2</v>
-      </c>
-      <c r="B13">
-        <v>0.527064665943998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14">
-        <v>3</v>
-      </c>
-      <c r="B14">
-        <v>0.527064665943998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
-        <v>4</v>
-      </c>
-      <c r="B15">
-        <v>0.5275470314612689</v>
+        <v>-465.8218814093863</v>
       </c>
     </row>
   </sheetData>
